--- a/research/brics_universities/output/BRICS_universities_partners.xlsx
+++ b/research/brics_universities/output/BRICS_universities_partners.xlsx
@@ -632,10 +632,10 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -660,10 +660,10 @@
         <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -688,10 +688,10 @@
         <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
         <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H10" t="n">
         <v>40</v>
@@ -744,10 +744,10 @@
         <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H11" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -772,7 +772,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" t="n">
         <v>15</v>
@@ -831,7 +831,7 @@
         <v>37</v>
       </c>
       <c r="H14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
@@ -3009,14 +3009,33 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Uganda Christian University, P.O. Box 4, Mukono, Uganda</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
+          <t>Plot 67-173, Mukono Hill, Bishop Tucker Road, P.O. Box 4, Mukono, Uganda</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>info@ucu.ac.ug</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Prof. Aaron Mushengyezi
+Vice Chancellor
+Общий ящик университета (info); альтернатива — registrar@ucu.ac.ug
+Обращение: Dear Professor Mushengyezi,</t>
+        </is>
+      </c>
       <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr"/>
-      <c r="N15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>info@ucu.ac.ug</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>+256 312 350 800</t>
+        </is>
+      </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
           <t>https://ucu.ac.ug</t>
@@ -3052,24 +3071,31 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD15" s="4" t="inlineStr"/>
+      <c r="AD15" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE15" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF15" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт ucu.ac.ug недоступен (ошибка DNS/502 прокси) — контакты не проверены
-• Ректор взят из базы IAU WHED (дата обновления неизвестна); по поиску — в должности с августа 2020
-• По поисковой выдаче: info@ucu.ac.ug, тел. +256 312 350 800 — не подтверждено на открытой странице
-• WHED указывает International Relations Officer: Elizabeth Balyejusa Kizito — актуальность не подтверждена
-• Частный (Англиканская церковь Уганды)</t>
+          <t>• Через curl сайт недоступен (DNS/502 прокси), открыт через WebFetch
+• Отдельный e-mail международного офиса на сайте не найден; WHED указывает International Relations Officer: Elizabeth Balyejusa Kizito — актуальность не подтверждена
+• Частный (Англиканская церковь Уганды)
+• Перепроверка: Через WebFetch открыт официальный сайт ucu.ac.ug (04.10.2026): ВК проф. Aaron Mushengyezi подтверждён новостью от 08.09.2026; адрес, info@ucu.ac.ug, registrar@ucu.ac.ug и тел. +256 312 350 800 подтверждены на странице Contact Us</t>
         </is>
       </c>
       <c r="AG15" s="4" t="inlineStr">
         <is>
-          <t>Https://whed.net/institutions/IAU-016984</t>
+          <t>• Https://ucu.ac.ug/contact-us/
+• Https://ucu.ac.ug/vice-chancellor/
+• Https://ucu.ac.ug/vice-chancellor-urges-new-students-to-embrace-excellence/
+• Https://ucu.ac.ug/partnerships/
+• Https://whed.net/institutions/IAU-016984</t>
         </is>
       </c>
       <c r="AH15" s="4" t="inlineStr">
@@ -5481,9 +5507,10 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>ФИО не найдено
+          <t>Prof. Bakhtiyorjon Akbaraliyev
+Rector, Andijan State University
 Приёмная (канцелярия) университета
-Обращение: Dear Head of the International Office,</t>
+Обращение: Dear Professor Akbaraliyev,</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr"/>
@@ -5539,16 +5566,18 @@
       </c>
       <c r="AE15" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF15" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт adu.uz закрыт защитой Cloudflare (403) — данные взяты из официального Telegram-канала (@adu_uz, сентябрь–октябрь 2026) и портала ZiyoNET
+          <t>• Официальный сайт adu.uz закрыт защитой Cloudflare (403) — данные взяты из официального Telegram-канала (@adu_uz) и госпортала ZiyoNET
+• Ректор Бахтиёржон Акбаралиев подтверждён официальным предупреждением в Telegram-канале вуза от 02.10.2026 (о поддельных аккаунтах от его имени — при переписке использовать только официальные каналы)
+• Адрес, телефон и qabulxona@adu.uz — по ZiyoNET, на сайте вуза не перепроверены
 • Отдельный e-mail международного отдела не найден; в новостях упоминается руководитель отдела международных связей «И. Хасанов» (полное имя не подтверждено)
-• В октябре 2026 г. вуз вёл переговоры с Воронежским государственным техническим университетом (Россия)
 • THE2027: в статусе Reporter (без ранга)
-• Быстрая проверка космической активности: запущенных университетских спутников в Узбекистане не найдено (первый национальный спутник ДЗЗ Samarkand-2028 выведен агентством «Узбеккосмос» в 2026 г.)</t>
+• Быстрая проверка космической активности: запущенных университетских спутников в Узбекистане не найдено
+• Перепроверка: 04.10.2026: ректор подтверждён официальным Telegram-каналом (02.10.2026); сайт по-прежнему за Cloudflare, контакты — по ZiyoNET</t>
         </is>
       </c>
       <c r="AG15" s="4" t="inlineStr">
@@ -6323,25 +6352,25 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>karsu_info@edu.uz</t>
+          <t>rector@karsu.uz</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
           <t>ФИО не найдено
-Общий ящик университета
+Приёмная ректора / общий ящик университета
 Обращение: Dear Head of the International Office,</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr"/>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>karsu_info@edu.uz</t>
+          <t>rector@karsu.uz; karsu_info@edu.uz</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>+998 55 105 60 48</t>
+          <t>+998 55 105 60 47 (приёмная ректора); +998 55 105 60 48 (колл-центр)</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -6351,7 +6380,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>Mr. Berdiyar Jollibekov</t>
+          <t>Prof. Berdiyar Baxtiyarovich Jollibekov (DSc in Agricultural Sciences)</t>
         </is>
       </c>
       <c r="Q21" s="4" t="inlineStr">
@@ -6386,20 +6415,23 @@
       </c>
       <c r="AE21" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF21" s="4" t="inlineStr">
         <is>
-          <t>• Сайт karsu.uz — SPA (Next.js); ректор Бердияр Жоллыбеков подтверждён новостями сайта и UzDaily (сентябрь 2026); ранее — ректор Каракалпакского института сельского хозяйства и агротехнологий; учёная степень не подтверждена
-• Полный почтовый адрес и международный e-mail на сайте не найдены; телефон — колл-центр
+          <t>• Сайт karsu.uz — SPA (Next.js), данные берутся из API; ректор Бердияр Бахтиярович Жоллыбеков (доктор сельскохозяйственных наук, профессор) подтверждён страницей руководства и новостями (сентябрь 2026); ранее — ректор Каракалпакского института сельского хозяйства и агротехнологий
+• Полный почтовый адрес и международный отдел/e-mail на сайте не найдены; +998 55 105 60 48 — колл-центр
 • THE2027: в статусе Reporter (без ранга)
-• Быстрая проверка космической активности: запущенных университетских спутников в Узбекистане не найдено (первый национальный спутник ДЗЗ Samarkand-2028 выведен агентством «Узбеккосмос» в 2026 г.)</t>
+• Быстрая проверка космической активности: запущенных университетских спутников в Узбекистане не найдено (первый национальный спутник ДЗЗ Samarkand-2028 выведен агентством «Узбеккосмос» в 2026 г.)
+• Перепроверка: Через API страницы «Administration» на karsu.uz 04.10.2026 подтверждены ректор Жоллыбеков Б.Б. (д.с.-х.н., профессор), rector@karsu.uz и тел. +998 55 105 60 47; международный отдел и полный адрес не найдены</t>
         </is>
       </c>
       <c r="AG21" s="4" t="inlineStr">
         <is>
-          <t>• Https://karsu.uz/en
+          <t>• Https://karsu.uz/en/administration
+• Https://karsu.uz/api/menus/admin/
+• Https://karsu.uz/en
 • Https://karsu.uz/api/news/posts/
 • Https://www.uzdaily.uz/en/karakalpak-state-university-signs-mou-with-chinese-delegation-19-09-2026/</t>
         </is>
@@ -6811,7 +6843,8 @@
 • Ректор Эргашев О.К. назначен постановлением Кабмина (новость yuz.uz, 2025 г.); учёная степень не указана
 • Сайт namdtu.uz — SPA с частично демонстрационными данными; e-mail info@namdtu.uz взят из кода сайта, телефон и адрес не подтверждены
 • THE2027: в статусе Reporter (без ранга)
-• Быстрая проверка космической активности: запущенных университетских спутников в Узбекистане не найдено (первый национальный спутник ДЗЗ Samarkand-2028 выведен агентством «Узбеккосмос» в 2026 г.)</t>
+• Быстрая проверка космической активности: запущенных университетских спутников в Узбекистане не найдено (первый национальный спутник ДЗЗ Samarkand-2028 выведен агентством «Узбеккосмос» в 2026 г.)
+• Перепроверка: Сайт namdtu.uz 04.10.2026 отдаёт пустой ответ (curl 200/0 байт, WebFetch 502); данные не изменены</t>
         </is>
       </c>
       <c r="AG24" s="4" t="inlineStr">
@@ -7017,41 +7050,46 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Navoi, Uzbekistan</t>
+          <t>103 Galaba Shoh Street, Navoiy, Uzbekistan</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>info@nspi.uz</t>
+          <t>info@nsu.uz</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>ФИО не найдено
-Общий ящик университета
-Обращение: Dear Head of the International Office,</t>
+          <t>Narzikulova Dilnoza Xoshimjonovna
+Проректор по международному сотрудничеству (Vice-Rector for International Cooperation)
+Общий ящик университета (info@nsu.uz)
+Обращение: Dear Vice-Rector Narzikulova,</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr"/>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>info@nspi.uz</t>
-        </is>
-      </c>
-      <c r="N26" s="4" t="inlineStr"/>
+          <t>info@nsu.uz</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>+998 79 223-77-89</t>
+        </is>
+      </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>https://nspi.uz</t>
+          <t>https://ndu.uz</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>Prof. Muhiddin Kalonov</t>
+          <t>Prof. Muxiddin Baxriddinovich Kalonov</t>
         </is>
       </c>
       <c r="Q26" s="4" t="inlineStr">
         <is>
-          <t>Rector, Professor</t>
+          <t>Rector, Doctor of Economics (DSc), Professor</t>
         </is>
       </c>
       <c r="R26" s="4" t="inlineStr"/>
@@ -7081,22 +7119,24 @@
       </c>
       <c r="AE26" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF26" s="4" t="inlineStr">
         <is>
-          <t>• Создан в 2024 г. на базе Навоийского государственного педагогического института; домен nspi.uz сейчас показывает страницу-заглушку хостинга
-• Ректор проф. Мухиддин Калонов и e-mail info@nspi.uz подтверждены официальным Telegram-каналом (@NavDU_NavSU, сентябрь–октябрь 2026)
-• Адрес (ул. Ибн Сино, 45) и телефон встречаются только во вторичных источниках — не подтверждены
-• Направления подготовки указаны ориентировочно (в Telegram упоминаются 7 факультетов, в т.ч. медицинский)
+          <t>• Направления подготовки указаны ориентировочно (в Telegram упоминаются 7 факультетов, в т.ч. медицинский)
 • THE2027: в статусе Reporter (без ранга)
-• Быстрая проверка космической активности: запущенных университетских спутников в Узбекистане не найдено (первый национальный спутник ДЗЗ Samarkand-2028 выведен агентством «Узбеккосмос» в 2026 г.)</t>
+• Быстрая проверка космической активности: запущенных университетских спутников в Узбекистане не найдено (первый национальный спутник ДЗЗ Samarkand-2028 выведен агентством «Узбеккосмос» в 2026 г.)
+• Создан в 2024 г. на базе Навоийского государственного педагогического института; актуальный сайт — ndu.uz (nspi.uz — заглушка хостинга)
+• В описании Telegram-канала всё ещё указан старый ящик info@nspi.uz; на сайте ndu.uz — info@nsu.uz (общий) и admission@nsu.uz (приём)
+• Перепроверка: 04.10.2026: найден актуальный сайт ndu.uz — ректор, адрес, телефон, e-mail info@nsu.uz и проректор по международному сотрудничеству подтверждены (© 2026)</t>
         </is>
       </c>
       <c r="AG26" s="4" t="inlineStr">
         <is>
-          <t>• Https://t.me/s/NavDU_NavSU
+          <t>• Https://ndu.uz/en/
+• Https://ndu.uz/en/international-office.html
+• Https://t.me/s/NavDU_NavSU
 • Https://kun.uz/news/2024/10/31/navoiy-davlat-universiteti-tashkil-etildi</t>
         </is>
       </c>
@@ -7653,10 +7693,11 @@
       <c r="AF30" s="4" t="inlineStr">
         <is>
           <t>• Бывший Самаркандский государственный архитектурно-строительный университет (SamDAQU); домен samdaqu.edu.uz перенаправляет на sdtu.uz
-• На странице ректора указано имя «Chidem Janbay Turkyilmaz» без степени и даты — требуется проверка перед отправкой; обращение оставлено нейтральным
+• Повторная проверка 04.10.2026: на странице ректора — «Chidem Janbay Turkyilmaz, Universitet Rektori» (тел. (0366) 237-15-93, samdaqu@samdaqu.edu.uz, ул. Лолазор, 70, индекс 140143); в новостях сайта упоминается «rektori Chidem Turkyilmaz» (меморандум с IT-Park), но новости и подвал сайта датированы 2022–2023 гг. — актуальность на 2026 г. не подтверждена; обращение оставлено нейтральным
 • Проректор по международным связям не указан; сайт international.samdaqu.edu.uz недоступен (ошибка SSL). Использовать samdaqu@samdaqu.edu.uz
 • THE2027: в статусе Reporter (без ранга)
-• Быстрая проверка космической активности: запущенных университетских спутников в Узбекистане не найдено (первый национальный спутник ДЗЗ Samarkand-2028 выведен агентством «Узбеккосмос» в 2026 г.)</t>
+• Быстрая проверка космической активности: запущенных университетских спутников в Узбекистане не найдено (первый национальный спутник ДЗЗ Samarkand-2028 выведен агентством «Узбеккосмос» в 2026 г.)
+• Перепроверка: Ректор и контакты повторно найдены на сайте, но содержимое сайта датировано 2022–2023 гг.; актуальность не подтверждена, данные не изменены</t>
         </is>
       </c>
       <c r="AG30" s="4" t="inlineStr">
@@ -7718,7 +7759,7 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>32 Navoi Street, Tashkent 100011, Uzbekistan</t>
+          <t>Navoiy ko‘chasi, 32-uy, Toshkent 100011, Uzbekistan (32 Navoi Street, Tashkent 100011)</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -7751,7 +7792,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>B. Sh. Usmonov</t>
+          <t>Botir Sh. Usmonov (Б.Ш. Усмонов)</t>
         </is>
       </c>
       <c r="Q31" s="4" t="inlineStr">
@@ -7786,15 +7827,17 @@
       </c>
       <c r="AE31" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF31" s="4" t="inlineStr">
         <is>
-          <t>• Сайт tkti.uz — SPA; контакты из официального API. Ректор указан только инициалами (Б.Ш. Усмонов) в новости АО «Узкимёсаноат» о выпуске 2026 г.; полное имя на официальной странице не подтверждено
-• Международный отдел/e-mail не найден
+          <t>• Сайт tkti.uz — SPA; главная открыта через r.jina.ai 04.10.2026, страницы ректората/международного отдела в reader-сервисе не отрисовываются (404). Ректор: инициалы Б.Ш. Усмонов (новость АО «Узкимёсаноат», выпуск 2026) + имя «Botir» из официальной ссылки «Rektor sahifasi» (домен botir-usmonov.com сейчас не резолвится); полное отчество не подтверждено
+• Проректоры (новости сайта): по академической деятельности — Т. Сафаров; по научной работе и инновациям — Х. Пулатов
+• Международный отдел/e-mail не найден (на сайте есть разделы International: partners, exchange, erasmus — без контактов в reader-версии)
 • THE2027: в статусе Reporter (без ранга)
-• Быстрая проверка космической активности: запущенных университетских спутников в Узбекистане не найдено (первый национальный спутник ДЗЗ Samarkand-2028 выведен агентством «Узбеккосмос» в 2026 г.)</t>
+• Быстрая проверка космической активности: запущенных университетских спутников в Узбекистане не найдено (первый национальный спутник ДЗЗ Samarkand-2028 выведен агентством «Узбеккосмос» в 2026 г.)
+• Перепроверка: Главная tkti.uz открыта через reader-сервис 04.10.2026: адрес, info@tkti.uz и телефон подтверждены; имя ректора уточнено по официальной ссылке «Rektor sahifasi» (Botir Usmonov), отчество полностью не подтверждено</t>
         </is>
       </c>
       <c r="AG31" s="4" t="inlineStr">
@@ -12529,7 +12572,8 @@
         <is>
           <t>• Частный университет группы Phenikaa; сайт — SPA, страницы руководства не отдают данные; ректор не подтверждён
 • В CMS сайта фигурирует ящик отдела внешних связей htdn@phenikaa-uni.edu.vn (не опубликован как контакт — использовать с осторожностью)
-• Космической деятельности не выявлено (быстрая проверка по nanosats.csv)</t>
+• Космической деятельности не выявлено (быстрая проверка по nanosats.csv)
+• Перепроверка: Сайт phenikaa-uni.edu.vn открыт (исправлена цепочка сертификата), но страница «Ban giám hiệu» подгружает данные на клиенте — ректор не подтверждён; данные не изменены (04.10.2026)</t>
         </is>
       </c>
       <c r="AG32" s="4" t="inlineStr">
@@ -13564,7 +13608,11 @@
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>VinUniversity, Vinhomes Ocean Park, Gia Lam, Hanoi, Vietnam (по поисковой выдаче; не открыто)</t>
+        </is>
+      </c>
       <c r="J40" s="4" t="inlineStr"/>
       <c r="K40" s="4" t="inlineStr"/>
       <c r="L40" s="4" t="inlineStr"/>
@@ -13575,8 +13623,16 @@
           <t>https://vinuni.edu.vn</t>
         </is>
       </c>
-      <c r="P40" s="4" t="inlineStr"/>
-      <c r="Q40" s="4" t="inlineStr"/>
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Le Mai Lan (Lê Mai Lan)</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="R40" s="4" t="inlineStr"/>
       <c r="S40" s="4" t="inlineStr"/>
       <c r="T40" s="4" t="inlineStr"/>
@@ -13605,9 +13661,11 @@
       </c>
       <c r="AF40" s="4" t="inlineStr">
         <is>
-          <t>• Сайт vinuni.edu.vn блокирует автоматический доступ (Cloudflare 403); квота веб-поиска исчерпана — контакты и руководство не проверены, требуется ручное заполнение
-• Частный университет группы Vingroup; имеет соглашение о сотрудничестве с USTH (новость на usth.edu.vn)
-• Космической деятельности не выявлено (быстрая проверка по nanosats.csv)</t>
+          <t>• Частный университет группы Vingroup; имеет соглашение о сотрудничестве с USTH (новость на usth.edu.vn)
+• Космической деятельности не выявлено (быстрая проверка по nanosats.csv)
+• Все сайты *.vinuni.edu.vn за Cloudflare (403, 04.10.2026). Президент Dr. Le Mai Lan и ответственный за международные связи Prof. Sunmee Choi (Vice Provost of External Engagement) — по карточке члена APRU (apru.org); проректор (Provost) — Prof. Tan Yap Peng (по выдаче, новость vingroup.net)
+• По поисковой выдаче (не открыто): общий e-mail info@vinuni.edu.vn, тел. +84 24 7108 9779 — в поля не внесены до проверки
+• Перепроверка: Сайт закрыт Cloudflare; по карточке APRU добавлены президент Dr. Le Mai Lan и адресат Prof. Sunmee Choi; e-mail не подтверждён</t>
         </is>
       </c>
       <c r="AG40" s="4" t="inlineStr">
@@ -13724,7 +13782,9 @@
           <t>• Официальный сайт vinhuni.edu.vn блокирует доступ (Cloudflare 403) — контакты не проверены
 • Ректор не подтверждён: GS.TS Nguyễn Huy Bằng был ректором на срок 2020–2025; по данным поиска в 2026 г. возможны изменения (Nguyễn Ngọc Hiền) — уточнить
 • Телефон — Отдел обучения/приёмная кампания (из документа о приёме 2026)
-• E-mail не найдены; космической деятельности не выявлено (быстрая проверка по nanosats.csv)</t>
+• E-mail не найдены; космической деятельности не выявлено (быстрая проверка по nanosats.csv)
+• Повторная проверка 04.10.2026: поисковая сводка называет ректором Nguyễn Ngọc Hiền (он же партсекретарь), но официальная страница не открылась — в поля не внесено
+• Перепроверка: Сайт vinhuni.edu.vn (включая поддомены) по-прежнему закрыт Cloudflare (403); ректор не подтверждён; данные не изменены</t>
         </is>
       </c>
       <c r="AG41" s="4" t="inlineStr">
@@ -16047,7 +16107,8 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>ФИО не найдено
+          <t>Assoc. Prof. Dr. Panavy Pookaiyaudom
+President
 Международный колледж (Mahanakorn University of Technology International College, MUTIC)
 Обращение: Dear Head of the International Office,</t>
         </is>
@@ -16060,22 +16121,22 @@
       <c r="M14" s="4" t="inlineStr"/>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>+66 61 223 2344</t>
+          <t>+66 2 988 3650 (ext. 1105–1107)</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>https://www.mut.ac.th</t>
+          <t>https://mut.ac.th</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>Prof. Panavy Pookaiyaudom</t>
+          <t>Assoc. Prof. Dr. Panavy Pookaiyaudom (รศ. ดร.ภานวีย์ โภไคยอุดม)</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>President (อธิการบดี)</t>
         </is>
       </c>
       <c r="R14" s="4" t="inlineStr"/>
@@ -16121,23 +16182,25 @@
       </c>
       <c r="AE14" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF14" s="4" t="inlineStr">
         <is>
-          <t>• Основной сайт www.mut.ac.th недоступен (ошибка TLS / HTTP 503); контакты взяты с сайта международного колледжа MUTIC (inter.mut.ac.th) — inter@mut.ac.th и тел. +66 61 223 2344 относятся к международному колледжу
-• Президент проф. Панави Пукайяудом подтверждён только источником от октября 2024 (визит в Chongqing Jiaotong University); Википедия называет другое имя (Sujate Jantarang) — перепроверить перед отправкой
-• Исторически первый тайский вуз со своим микроспутником TMSAT (Thai Paht-1, 1998), построенным инженерами MUT в Университете Суррея; данные о TMSAT из Википедии, официальную страницу открыть не удалось
-• Частный университет</t>
+          <t>• Сайт mut.ac.th открывается (неполная цепочка сертификата устранена загрузкой промежуточного сертификата Sectigo); на странице «Руководство» (staff-manager, сайт 2025–2026) президент — доц. д-р Панави Пукайяудом; Sujate Jantarang — теперь советник президента
+• Телефон и адрес — со страницы «Контакты» mut.ac.th (общий номер, доб. 1105–1107 — отдел по связям с общественностью); общего e-mail на сайте нет
+• Inter@mut.ac.th — ящик международного колледжа MUTIC из прежней проверки; новый сайт inter.mut.ac.th (2026) e-mail не показывает — перепроверить
+• Исторически первый тайский вуз со своим микроспутником TMSAT (Thai Paht-1, 1998), построенным инженерами MUT в Университете Суррея; данные о TMSAT из Википедии
+• Частный университет
+• Перепроверка: Президент (доц. д-р Панави Пукайяудом), адрес и телефон подтверждены на сайте mut.ac.th 04.10.2026; e-mail MUTIC не подтверждён</t>
         </is>
       </c>
       <c r="AG14" s="4" t="inlineStr">
         <is>
-          <t>• Https://en.wikipedia.org/wiki/Mahanakorn_University_of_Technology
-• Https://inter.mut.ac.th/privacy-policy/
-• Https://inter.mut.ac.th/about-us/
-• Https://www.cqjtu.edu.cn/info/1178/1851.htm</t>
+          <t>• Https://mut.ac.th/staff-manager/
+• Https://mut.ac.th/contact-us/
+• Https://en.wikipedia.org/wiki/Mahanakorn_University_of_Technology
+• Https://inter.mut.ac.th/privacy-policy/</t>
         </is>
       </c>
       <c r="AH14" s="4" t="inlineStr">
@@ -16538,22 +16601,27 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>120 The Government Complex, Ratthaprasasanabhakti Building, 6th–7th Floor, Chaeng Watthana Road, Lak Si, Bangkok 10210, Thailand</t>
+          <t>120 Government Complex Commemorating His Majesty the King's 80th Birthday Anniversary, Ratthaprasasanabhakti Building, 6th–7th Floors, Chaeng Watthana Road, Thung Song Hong, Lak Si, Bangkok 10210, Thailand</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>saraban@gistda.or.th</t>
+          <t>siriluk@gistda.or.th</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>ФИО не найдено
+          <t>Dr. Pakorn Apaphant
+Executive Director (ceo@gistda.or.th, +66 2 141 4450)
 Отдел делопроизводства / официальной корреспонденции (Saraban)
-Обращение: Dear Head of the International Office,</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr"/>
+Обращение: Dear Dr. Apaphant,</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>siriluk@gistda.or.th</t>
+        </is>
+      </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
           <t>saraban@gistda.or.th</t>
@@ -16631,23 +16699,26 @@
       </c>
       <c r="AE17" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF17" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт gistda.or.th был недоступен (HTTP 503 / ошибка TLS); адрес, телефон и e-mail saraban@gistda.or.th взяты из поисковой выдачи по странице контактов GISTDA — перед рассылкой перепроверить
+          <t>• Официальный сайт открывается только по http:// (у https ошибка сертификата); адрес, телефоны 0-2141-4444/4468 и saraban@gistda.or.th подтверждены в подвале главной страницы (новости сентября 2026)
+• Исполнительный директор Pakorn Apaphant, Ph.D. — на официальной странице «Executive Team»: тел. +66 2 141 4450, ceo@gistda.or.th
+• Email_international — заместитель исполнительного директора по стратегическим альянсам (Strategic Alliance Engagement) Siriluk Prukpitikul, Ph.D., тел. +66 2 141 4665; отдельного ящика международного отдела нет
 • GISTDA — национальное космическое агентство Таиланда: владеет и эксплуатирует THEOS (2008) и THEOS-2 (2023), но оба построены Airbus/EADS, поэтому в satellites_launched не засчитаны
 • THEOS-2A (совместная разработка) потерян при аварии PSLV-C62 12.01.2026; THEOS-3 разрабатывается тайскими инженерами
-• Директор д-р Пакорн Апапхан (ปกรณ์ อาภาพันธุ์) упомянут в новости от 4.09.2026
-• 25.08.2026 на Long March-6C выведен GISTDA CubeSat-1 (Lingzhi-09), разработанный китайской GalaxySpace для GISTDA (с наземным сегментом и обучением тайской команды) — не засчитан как собственная разработка; спутник предназначен в т.ч. для обучения студентов тайских вузов</t>
+• 25.08.2026 на Long March-6C выведен GISTDA CubeSat-1 (Lingzhi-09), разработанный китайской GalaxySpace для GISTDA — не засчитан как собственная разработка
+• Перепроверка: Сайт открыт по http 04.10.2026: директор, адрес, телефон и e-mail подтверждены на официальных страницах; добавлены ceo@ и ящик зам. директора по стратегическим альянсам</t>
         </is>
       </c>
       <c r="AG17" s="4" t="inlineStr">
         <is>
-          <t>• Https://en.wikipedia.org/wiki/Geo-Informatics_and_Space_Technology_Development_Agency
+          <t>• Http://www.gistda.or.th/
+• Http://www.gistda.or.th/about/organizational-structure-gistda-board-structure-gistda-executive-team/
+• Https://en.wikipedia.org/wiki/Geo-Informatics_and_Space_Technology_Development_Agency
 • Https://thestandard.co/thailand-space-market-theos3-law/
-• Https://www.gistda.or.th/news_view_new.php?n_id=9176
 • Https://www.mreport.co.th/news/industry-movement/316-kmitl-launches-space-hub-chumporn
 • Https://equalocean.com/news/2026082622141-galaxyspace-completes-first-whole-satellite-delivery-southeast-asia-thai-cubesat</t>
         </is>
@@ -21390,7 +21461,8 @@
           <t>• Сайт mslu.by недоступен из нашей среды (ошибка прокси 502 / DNS), контакты и ректор не проверены — заполнить вручную перед рассылкой
 • Лингвистический профиль — космическая тематика маловероятна; возможна роль партнёра по языковой подготовке
 • Спутниковых проектов не найдено (быстрая проверка по nanosats.csv/поиску)
-• В выгрузках санкционных списков EU/UK/OFAC/US Entity List вуз и ректор не найдены; учитывать общий санкционный режим ЕС в отношении Беларуси</t>
+• В выгрузках санкционных списков EU/UK/OFAC/US Entity List вуз и ректор не найдены; учитывать общий санкционный режим ЕС в отношении Беларуси
+• Перепроверка: Сайт mslu.by по-прежнему недоступен (04.10.2026: ошибка прокси 502 / DNS, WebFetch — EAI_AGAIN); на сайте Минобразования РБ данных о ректоре нет; данные не изменены</t>
         </is>
       </c>
       <c r="AG23" s="4" t="inlineStr">
@@ -23125,7 +23197,11 @@
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>+591 3 336 5533; +591 3 336 5544</t>
+        </is>
+      </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
           <t>https://www.uagrm.edu.bo</t>
@@ -23164,22 +23240,25 @@
       <c r="AD6" s="4" t="inlineStr"/>
       <c r="AE6" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF6" s="4" t="inlineStr">
         <is>
-          <t>• Ректор указан на странице ректората (без даты)
-• Общий e-mail, адрес и телефон ректората на сайте не найдены; страница 'Contacto' содержит только контакты по факультетам (центры обработки данных)
-• Международный офис не найден
-• Быстрая проверка космической активности (nanosats.csv + сайт): спутников не обнаружено</t>
+          <t>• Ректор Dr. Reinerio Vargas Banegas указан на официальной странице ректората; срок полномочий 2025–2029 (вступил в должность 23.09.2025), упоминается как ректор в СМИ в 2026 г
+• Телефоны (591-3) 336-5533 / 336-5544 и факс 334-2160 — из подвала официального сайта (без указания подразделения)
+• Общий e-mail и точный почтовый адрес ректората на сайте не найдены; страница 'Contacto' содержит только контакты факультетских CPD
+• Международные связи — подразделение RPNI (Relaciones Públicas Nacionales e Internacionales), страница /unidades-administrativas/rpni отдаёт 403 — контакты не получены
+• Быстрая проверка космической активности (nanosats.csv + сайт): спутников не обнаружено
+• Перепроверка: Ректор подтверждён на сайте и в СМИ 2026 г. (срок 2025–2029); добавлен телефон с официального сайта 04.10.2026; e-mail не найден</t>
         </is>
       </c>
       <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uagrm.edu.bo/
 • Https://www.uagrm.edu.bo/unidades-administrativas/rectorado
-• Https://www.uagrm.edu.bo/contacto</t>
+• Https://www.uagrm.edu.bo/contacto
+• Https://eju.tv/2026/08/rector-de-la-uagrm-pide-al-gobierno-sincerarse-y-ofrece-apoyo-cientifico-de-las-universidades/</t>
         </is>
       </c>
       <c r="AH6" s="4" t="inlineStr">
@@ -23823,7 +23902,11 @@
           <t>informaciones@uatf.edu.bo</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr"/>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>+591 2 6227300 (Rectorado); Relaciones Públicas e Internacionales: +591 2 6227730</t>
+        </is>
+      </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
           <t>https://www.uatf.edu.bo</t>
@@ -23867,14 +23950,17 @@
       </c>
       <c r="AF11" s="4" t="inlineStr">
         <is>
-          <t>• Сайт — одностраничное JS-приложение; имя ректора, телефоны и международный офис извлечь не удалось
-• Адрес и e-mail взяты из кода сайта (футер)
-• Быстрая проверка космической активности (nanosats.csv + сайт): спутников не обнаружено</t>
+          <t>• Сайт — одностраничное JS-приложение; имя ректора и e-mail международного офиса извлечь не удалось
+• Адрес и e-mail взяты из кода сайта (футер); телефоны — из официального телефонного справочника (API swservice.uatf.edu.bo, обновлён в 2022 г., возможна неактуальность)
+• Есть подразделение «Relaciones Públicas e Internacionales» (тел. 6227730), e-mail не найден
+• Быстрая проверка космической активности (nanosats.csv + сайт): спутников не обнаружено
+• Перепроверка: Из официального API-справочника сайта (swservice.uatf.edu.bo, записи 2022 г.) добавлены телефоны ректората и отдела по связям с общественностью и международным связям; имя ректора на официальных страницах по-прежнему не найдено</t>
         </is>
       </c>
       <c r="AG11" s="4" t="inlineStr">
         <is>
-          <t>Https://www.uatf.edu.bo/</t>
+          <t>• Https://www.uatf.edu.bo/
+• Https://swservice.uatf.edu.bo/api/agenda/type (официальный телефонный справочник UATF, записи 2022 г.)</t>
         </is>
       </c>
       <c r="AH11" s="4" t="inlineStr">
@@ -24453,20 +24539,43 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Carretera a Camajuaní km 5½, 50100 Santa Clara, Villa Clara, Cuba</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
+          <t>Carretera a Camajuaní km 5½, Santa Clara, Villa Clara, Cuba</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>yanelysd@uclv.edu.cu</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Dra. Yanelys Delgado Triana
+Директор по международным связям (Directora de Relaciones Internacionales)
+Директор по международным связям (Dirección de Relaciones Internacionales)
+Обращение: Dear Dr. Delgado Triana,</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>yanelysd@uclv.edu.cu</t>
+        </is>
+      </c>
       <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>+53 42 281618 (Dirección de Relaciones Internacionales); +53 42 281417 (Secretaría General)</t>
+        </is>
+      </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
           <t>https://www.uclv.edu.cu</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>Dr. C. Luis Antonio Barranco Olivera</t>
+        </is>
+      </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Rector</t>
@@ -24492,19 +24601,23 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr"/>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE4" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF4" s="4" t="inlineStr">
         <is>
-          <t>• Сайты кубинских вузов (.cu) недоступны из нашей сети (503/сброс соединения) — контакты из сторонних каталогов (uniRank, Grupo La Rábida, Wikipedia, Cubadebate)
-• Ректор не подтверждён: англ. Википедия — Dr. Osana Molerio Pérez, исп. Википедия/поиск — Dr. C. Luis Antonio Barranco Olivera; уточнить перед отправкой
-• E-mail и телефоны не найдены на доступных страницах
+          <t>• Сайт uclv.edu.cu напрямую из нашей сети недоступен; страницы (главная, «Internacionalización») открыты через r.jina.ai 04.10.2026. Почтовый индекс 50100 на официальной странице не указан (взят ранее из каталогов) — удалён из адреса
+• Заместитель директора по междунар. связям: Nosley Pérez Castellano (nosleypc@uclv.cu, 42 281410); методист по междунар. сотрудничеству: Milagros Sarduy Valdés (milagrossv@uclv.edu.cu). Есть офис UCLV в Китае (Чжэнчжоу), oficinachina@uclv.edu.cu
 • Быстрая проверка космической активности (поиск + nanosats.csv): спутников не обнаружено
-• Куба под санкциями США (эмбарго) — учитывать при выборе платёжных/логистических схем</t>
+• Куба под санкциями США (эмбарго) — учитывать при выборе платёжных/логистических схем
+• Перепроверка: Ректор (Luis Antonio Barranco Olivera), директор по международным связям (e-mail, тел.) и адрес подтверждены на uclv.edu.cu 04.10.2026 (через reader-сервис)</t>
         </is>
       </c>
       <c r="AG4" s="4" t="inlineStr">
@@ -24566,7 +24679,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Instituto de Geofísica y Astronomía, La Habana, Cuba</t>
+          <t>Instituto de Geofísica y Astronomía, Calle 212 No. 2906, e/ 29 y 31, Rpto. La Coronela, La Lisa, La Habana, CP 11600, Cuba</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr"/>
@@ -24613,16 +24726,20 @@
       </c>
       <c r="AF5" s="4" t="inlineStr">
         <is>
-          <t>• Сайт iga.cu недоступен из нашей сети (503) как и все сайты .cu; квота веб-поиска исчерпана — директор, адрес, e-mail и телефоны не установлены
-• Существование и сайт подтверждены реестром ROR (ror.org/05e5m0q38)
+          <t>• Сайт iga.cu и все сайты .cu (granma.cu, ecured.cu) по-прежнему недоступны из нашей сети (503 / сброс соединения) — страницы не открыты
+• По поисковой выдаче (вероятно, страница iga.cu/quienes, дата не установлена): директор — Lic. Zulia Bárcena Fonseca, тел. приёмной директора 72714331 (+53 7 271 4331) — НЕ ПРОВЕРЕНО, в поля не внесено; адрес внесён по той же выдаче
+• Существование и сайт подтверждены реестром ROR (ror.org/05e5m0q38); институт активен в 2026 г. (публикации Granma 08.2026, cuba.cu 04.2026)
 • Подведомственность (по-видимому, Агентство по окружающей среде AMA / министерство CITMA) не подтверждена
 • Спутников, построенных институтом, не обнаружено (nanosats.csv); наземные станции/сотрудничество с агентствами не проверены
-• Куба под санкциями США (эмбарго)</t>
+• Куба под санкциями США (эмбарго)
+• Перепроверка: Сайты .cu недоступны; по поисковой выдаче добавлен адрес, имя директора и телефон — только в примечаниях, не проверены</t>
         </is>
       </c>
       <c r="AG5" s="4" t="inlineStr">
         <is>
-          <t>Https://ror.org/05e5m0q38</t>
+          <t>• Https://ror.org/05e5m0q38
+• Https://www.iga.cu/quienes/ (по поисковому индексу)
+• Https://www.granma.cu/ciencia/2026-08-24/reconocimiento-internacional-para-el-instituto-de-geofisica-y-astronomia (заголовок в выдаче)</t>
         </is>
       </c>
       <c r="AH5" s="4" t="inlineStr">
@@ -24751,7 +24868,8 @@
 • Ректор Julio Madera Quintana — по Cubadebate (поисковая выдача, дата не установлена) и исп. Википедии; каталог Grupo La Rábida указывает устаревшего ректора (Santiago Lajes Choy)
 • E-mail driuc@reduc.edu.cu (Дирекция межд. отношений) — из каталога La Rábida, дата неизвестна
 • Быстрая проверка космической активности (поиск + nanosats.csv): спутников не обнаружено
-• Куба под санкциями США (эмбарго) — учитывать при выборе платёжных/логистических схем</t>
+• Куба под санкциями США (эмбарго) — учитывать при выборе платёжных/логистических схем
+• Перепроверка: Сайт reduc.edu.cu и портал МВО Кубы mes.gob.cu недоступны (503 / сброс соединения, WebFetch 503) — данные не изменены (04.10.2026)</t>
         </is>
       </c>
       <c r="AG6" s="4" t="inlineStr">
@@ -24888,16 +25006,18 @@
       </c>
       <c r="AF7" s="4" t="inlineStr">
         <is>
-          <t>• Сайты кубинских вузов (.cu) недоступны из нашей сети (503/сброс соединения) — контакты из сторонних каталогов (uniRank, Grupo La Rábida, Wikipedia, Cubadebate)
-• Ректор Aniuska Ortiz Pérez — по каталогу Grupo La Rábida и исп. Википедии (дата не установлена; не подтверждено источником 2025–2026)
+          <t>• Сайты кубинских вузов (.cu) недоступны из нашей сети (503/сброс соединения, повторно 04.10.2026) — контакты из сторонних каталогов (uniRank, Grupo La Rábida, Wikipedia, Cubadebate); rector@uho.edu.cu не подтверждён
+• Ректор Aniuska Ortiz Pérez — действующая в 2026 г. по поисковой выдаче официальных новостей uho.edu.cu (выпуск 09.07.2026) и Radio Angulo (01.07.2026); страницы не открыты
 • Быстрая проверка космической активности (поиск + nanosats.csv): спутников не обнаружено
-• Куба под санкциями США (эмбарго) — учитывать при выборе платёжных/логистических схем</t>
+• Куба под санкциями США (эмбарго) — учитывать при выборе платёжных/логистических схем
+• Перепроверка: Ректор Aniuska Ortiz Pérez — действующая по выдаче официальных новостей uho.edu.cu и Radio Angulo (07.2026); сайты .cu по-прежнему недоступны — контакты не подтверждены</t>
         </is>
       </c>
       <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>• Https://www.grupolarabida.org/universidad/universidad-de-holguin-uho-cuba/
-• Https://es.wikipedia.org/wiki/Universidad_de_Holgu%C3%ADn</t>
+• Https://es.wikipedia.org/wiki/Universidad_de_Holgu%C3%ADn
+• Https://www.radioangulo.cu/2026/07/01/participa-rectora-de-universidad-de-holguin-en-foro-de-educacion-superior-en-brasil/ (snippet)</t>
         </is>
       </c>
       <c r="AH7" s="4" t="inlineStr">
@@ -24956,17 +25076,40 @@
           <t>Carretera a San Antonio de los Baños km 2½, Torrens, Boyeros, La Habana, Cuba</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>rector@uci.cu</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Dr. C. Raydel Montesino Perurena
+Ректор
+Ректор (по справочнику Grupo La Rábida)
+Обращение: Estimado Dr. Montesino:</t>
+        </is>
+      </c>
       <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>rector@uci.cu</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>+53 7 837 2548</t>
+        </is>
+      </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
           <t>https://www.uci.cu</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>Dr. C. Raydel Montesino Perurena</t>
+        </is>
+      </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>Rector</t>
@@ -24992,19 +25135,24 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD8" s="4" t="inlineStr"/>
+      <c r="AD8" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE8" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>• Сайты кубинских вузов (.cu) недоступны из нашей сети (503/сброс соединения) — контакты из сторонних каталогов (uniRank, Grupo La Rábida, Wikipedia, Cubadebate)
-• Ректор по поисковой выдаче с uci.cu — Dr. C. Raydel Montesino Perurena; страница не открылась — не подтверждено
-• E-mail и телефоны не найдены на доступных страницах
 • Быстрая проверка космической активности (поиск + nanosats.csv): спутников не обнаружено
-• Куба под санкциями США (эмбарго) — учитывать при выборе платёжных/логистических схем</t>
+• Куба под санкциями США (эмбарго) — учитывать при выборе платёжных/логистических схем
+• Сайт uci.cu по-прежнему недоступен (503, 04.10.2026). Ректор Raydel Montesino Perurena подтверждён репортажем Prensa Latina от 28.05.2026 (визит президента Díaz-Canel) и справочником ассоциации Grupo La Rábida
+• E-mail rector@uci.cu и тел. (7) 837 2548 — из справочника Grupo La Rábida (дата обновления не указана); там же муниципалитет указан как La Lisa (а не Boyeros) — уточнить
+• Перепроверка: Ректор подтверждён Prensa Latina (05.2026) и Grupo La Rábida; добавлены rector@uci.cu и телефон из справочника La Rábida; сайт вуза недоступен</t>
         </is>
       </c>
       <c r="AG8" s="4" t="inlineStr">
@@ -25120,7 +25268,8 @@
 • Ректор подтверждена Cubadebate (май 2024) — более свежего подтверждения нет
 • Полный почтовый адрес, e-mail и телефоны не найдены на доступных страницах
 • Быстрая проверка космической активности (поиск + nanosats.csv): спутников не обнаружено
-• Куба под санкциями США (эмбарго) — учитывать при выборе платёжных/логистических схем</t>
+• Куба под санкциями США (эмбарго) — учитывать при выборе платёжных/логистических схем
+• Перепроверка: 04.10.2026: umcc.cu по-прежнему недоступен (https — нет соединения, http — 503); данные не изменены</t>
         </is>
       </c>
       <c r="AG9" s="4" t="inlineStr">
@@ -25237,7 +25386,8 @@
 • Ректор Diana Sedal Yanes (назначена в 2017, упоминалась в 2023) — по исп. Википедии; англ. Википедия называет Zaida Valdés Estrada; актуальность на 2025–2026 не подтверждена
 • E-mail и телефоны не найдены на доступных страницах
 • Быстрая проверка космической активности (поиск + nanosats.csv): спутников не обнаружено
-• Куба под санкциями США (эмбарго) — учитывать при выборе платёжных/логистических схем</t>
+• Куба под санкциями США (эмбарго) — учитывать при выборе платёжных/логистических схем
+• Перепроверка: Сайты .cu (uo.edu.cu, mes.gob.cu, ecured.cu, cubadebate.cu) по-прежнему недоступны 04.10.2026; данные не изменены</t>
         </is>
       </c>
       <c r="AG10" s="4" t="inlineStr">
@@ -25355,7 +25505,8 @@
 • Ректор 'Yorki Mayor' по Cubadebate (декабрь 2024); полное имя и учёная степень не указаны
 • E-mail и телефоны не найдены на доступных страницах
 • Быстрая проверка космической активности (поиск + nanosats.csv): спутников не обнаружено
-• Куба под санкциями США (эмбарго) — учитывать при выборе платёжных/логистических схем</t>
+• Куба под санкциями США (эмбарго) — учитывать при выборе платёжных/логистических схем
+• Перепроверка: Сайт upr.edu.cu и сайт МВО Кубы (mes.gob.cu) по-прежнему недоступны (04.10.2026); данные не изменены</t>
         </is>
       </c>
       <c r="AG11" s="4" t="inlineStr">
@@ -27162,12 +27313,33 @@
 • Land management and geodesy</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr"/>
-      <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>пр. Женис, 62, Астана 010000, Казахстан (62 Zhenis Ave., Astana 010000, Kazakhstan)</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>office@kazatu.edu.kz</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>ФИО не найдено
+Обращение: Dear Head of the International Office,</t>
+        </is>
+      </c>
       <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>office@kazatu.edu.kz</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>+7 7172 31 75 47 (приёмная ректора)</t>
+        </is>
+      </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
           <t>https://kazatu.edu.kz</t>
@@ -27175,7 +27347,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>Prof. Kanat Tireuov</t>
+          <t>Prof. Kanat Maratovich Tireuov</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
@@ -27207,7 +27379,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD12" s="4" t="inlineStr"/>
+      <c r="AD12" s="4" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
       <c r="AE12" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
@@ -27215,16 +27391,18 @@
       </c>
       <c r="AF12" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт kazatu.edu.kz недоступен из нашей среды (DNS/таймаут) — адрес, e-mail и телефон не проверены, поля оставлены пустыми; по данным поиска: пр. Женис 62, Астана 010000, тел. +7 7172 31 75 47 — требуется проверка
-• Ректор подтверждён только внешними источниками 2025 г. (IOFS, OCA Magazine)
-• Космической активности не найдено (быстрая проверка)</t>
+          <t>• Официальный сайт kazatu.edu.kz недоступен из нашей среды (DNS/502); адрес, e-mail office@kazatu.edu.kz и телефон приёмной ректора +7 7172 31 75 47 взяты из поисковой выдачи по странице kazatu.edu.kz/ru/contacts — перепроверить перед рассылкой
+• Ректор К.М. Тиреуов (Председатель Правления – Ректор НАО) — по выдаче официального сайта и внешним источникам 2025 г. (IOFS, OCA Magazine)
+• Космической активности не найдено (быстрая проверка)
+• Перепроверка: Сайт kazatu.edu.kz по-прежнему недоступен (DNS/502); адрес, office@kazatu.edu.kz, телефон приёмной и ректор К.М. Тиреуов внесены по выдаче официальных страниц (kazatu.edu.kz/ru/contacts), не открытых напрямую</t>
         </is>
       </c>
       <c r="AG12" s="4" t="inlineStr">
         <is>
           <t>• Https://iofs.org/news/iofs-director-general-visits-saken-seifullin-kazakh-agrotechnical-research-university-to-strengthen-cooperation
 • Https://www.ocamagazine.com/2025/06/26/transforming-saken-seifullin-katru-from-a-research-university-to-a-world-class-institution-in-agriculture/
-• Nanosats.csv</t>
+• Nanosats.csv
+• Https://kazatu.edu.kz/ru/contacts (search snippet)</t>
         </is>
       </c>
       <c r="AH12" s="4" t="inlineStr">
@@ -28732,7 +28910,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>Государственный (НАО) — не проверено</t>
+          <t>Государственный (некоммерческое акционерное общество с единственным акционером; в совете директоров — представители Минтуризма и спорта и Минфина РК)</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -28815,21 +28993,24 @@
       </c>
       <c r="AE23" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF23" s="4" t="inlineStr">
         <is>
           <t>• Профиль — туризм и гостеприимство; космической активности не найдено (быстрая проверка) — низкий приоритет для спутникового проекта
-• ФИО ректора на странице руководства не указано (только вице-ректоры); телефон на сайте не найден
-• Вице-ректор по социальному развитию и международному сотрудничеству — Bekezhan Myrzayev (b.myrzaev@iuth.edu.kz)
-• Форма собственности не проверена</t>
+• ФИО ректора на странице «Басшылық» по-прежнему не указано (только вице-ректоры Л.И. Шалабаева и Б.К. Мырзаев); телефон на сайте не найден
+• Адрес (Туркестан, ул. Рабиги Султан Бегим 14А) и kense@iuth.edu.kz подтверждены на официальном сайте; руководитель отдела международного сотрудничества Әсел Дильмуратқызы (каб. 114, a.dilmuratkyzy@iuth.edu.kz) подтверждена на странице отдела
+• Вице-ректор по социальному развитию и международному сотрудничеству — Мырзаев Бекежан Кожабекович (b.myrzaev@iuth.edu.kz)
+• Форма собственности: НАО (КЕАҚ) с единственным акционером, совет директоров с госпредставителями (страница «Директорлар кеңесі», назначения 2025–2026)
+• Перепроверка: 04.10.2026: адрес, общий e-mail и контакт международного отдела подтверждены на сайте; уточнена форма собственности (НАО); ректор на сайте не назван</t>
         </is>
       </c>
       <c r="AG23" s="4" t="inlineStr">
         <is>
           <t>• Https://iuth.edu.kz/
 • Https://iuth.edu.kz/basshylyk/
+• Https://iuth.edu.kz/direktorlar-kenesi/
 • Https://iuth.edu.kz/halyqaraly-yntymaktastyk-bolimi/
 • Nanosats.csv</t>
         </is>
@@ -30184,21 +30365,48 @@
 • Construction</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr"/>
-      <c r="J33" s="4" t="inlineStr"/>
-      <c r="K33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>ул. Шевченко, 97, г. Алматы, Казахстан (97 Shevchenko St., Almaty, Kazakhstan)</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>info@alt.edu.kz</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>Сергазин Ғани Құдайбергенұлы (PhD)
+Vice-Rector for Research and International Cooperation
+Rector's office (rector@alt.edu.kz) / general info
+Обращение: Dear Vice-Rector,</t>
+        </is>
+      </c>
       <c r="L33" s="4" t="inlineStr"/>
-      <c r="M33" s="4" t="inlineStr"/>
-      <c r="N33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>info@alt.edu.kz</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>+7 707 888 1931</t>
+        </is>
+      </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
           <t>https://alt.edu.kz</t>
         </is>
       </c>
-      <c r="P33" s="4" t="inlineStr"/>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>Жармагамбетова Меруерт Советовна (Merueyrt Zharmagambetova), к.т.н., доцент</t>
+        </is>
+      </c>
       <c r="Q33" s="4" t="inlineStr">
         <is>
-          <t>Rector</t>
+          <t>Председатель Правления – Ректор (Chair of the Management Board – Rector)</t>
         </is>
       </c>
       <c r="R33" s="4" t="inlineStr"/>
@@ -30225,22 +30433,32 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD33" s="4" t="inlineStr"/>
+      <c r="AD33" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE33" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF33" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт alt.edu.kz недоступен (HTTP 503 / сброс соединения), квота веб-поиска исчерпана — контакты, руководство и форма собственности не проверены, поля пустые
-• Профиль (транспорт и связь, бывш. КазАТК) указан по общеизвестным данным — требует проверки
-• В nanosats.csv спутников вуза нет</t>
+          <t>• Руководство (страница «Руководство»): Председатель Правления – Ректор Жармагамбетова Меруерт Советовна, e-mail rector@alt.edu.kz; проректор по науке и международному сотрудничеству — Сергазин Ғани Құдайбергенұлы, на сайте при нём указан e-mail g.balbayev@alt.edu.kz (несоответствие фамилии — перед использованием уточнить)
+• Должность директора Департамента международного сотрудничества была вакантной (объявление от 21.05.2026) — отдельный международный e-mail не найден
+• Форма собственности не проверена (руководство через Правление — вероятно, акционерное общество)
+• Профиль — транспорт и связь (бывш. КазАТК), подтверждается структурой школ (инженерия, технологии, логистика и бизнес); 95-летие вуза в 2026 г
+• В nanosats.csv спутников вуза нет
+• Перепроверка: Сайт alt.edu.kz открыт 04.10.2026: ректор (Жармагамбетова М.С., rector@alt.edu.kz), проректор по науке и международному сотрудничеству, адрес, телефон и info@ подтверждены на официальных страницах (новости от 01–02.10.2026)</t>
         </is>
       </c>
       <c r="AG33" s="4" t="inlineStr">
         <is>
-          <t>Nanosats.csv</t>
+          <t>• Https://alt.edu.kz/ru/rukovodstvo/
+• Https://alt.edu.kz/ru/
+• Https://alt.edu.kz/ru/vakansiya/direktor-departamenta-mezhdunarodnogo-sotrudnichestva/
+• Nanosats.csv</t>
         </is>
       </c>
       <c r="AH33" s="4" t="inlineStr">
@@ -30294,11 +30512,33 @@
           <t>55 Zhandosov Street, Almaty 050035, Republic of Kazakhstan</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr"/>
-      <c r="K34" s="4" t="inlineStr"/>
-      <c r="L34" s="4" t="inlineStr"/>
-      <c r="M34" s="4" t="inlineStr"/>
-      <c r="N34" s="4" t="inlineStr"/>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>global@narxoz.kz</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>ФИО не найдено
+International Office (global@narxoz.kz)
+Обращение: Dear Head of the International Office,</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>global@narxoz.kz</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>narxoz@narxoz.kz</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>+7 727 377 11 11 (student service centre); International: +7 727 377 12 97</t>
+        </is>
+      </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
           <t>https://narxoz.edu.kz</t>
@@ -30338,23 +30578,30 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD34" s="4" t="inlineStr"/>
+      <c r="AD34" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE34" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF34" s="4" t="inlineStr">
         <is>
           <t>• Бизнес-университет; космической активности не найдено (быстрая проверка) — низкий приоритет
-• Сайт — SPA, контакты (e-mail, телефоны, International Office) подгружаются динамически и не извлечены; данные о ректоре и адресе взяты из кода сайта
-• Форма собственности не проверена</t>
+• Контакты подтверждены через официальный API сайта (страница «Контакты», 04.10.2026): общий narxoz@narxoz.kz, адрес ул. Жандосова, 55, Алматы 050035; International — global@narxoz.kz, +7 727 377 12 97; пресс-служба Pr@narxoz.kz
+• Ректор Канат Кожахмет — по коду сайта; поиск по сайту находит его упоминания в новостях 06–08.2026, но страницы руководства в API нет — должность/текст новостей не открыты
+• Форма собственности не проверена (на сайте упоминается НАО «Университет Нархоз» с Советом директоров)
+• Перепроверка: Общий и международный e-mail, телефоны и адрес подтверждены через официальный API сайта 04.10.2026; ректор — по коду сайта и новостям 2026 г</t>
         </is>
       </c>
       <c r="AG34" s="4" t="inlineStr">
         <is>
           <t>• Https://narxoz.edu.kz/
-• Https://narxoz.edu.kz/assets/index-C-Pmxz2y.js
+• Https://narxoz.edu.kz/contacts (API: https://narxoz.edu.kz/api/v1/pages/contacts/)
+• Https://narxoz.edu.kz/api/v1/search/?q=Кожахмет
 • Nanosats.csv</t>
         </is>
       </c>
@@ -31355,7 +31602,8 @@
           <t>• Сайт рендерит контакты и руководство динамически — ФИО первого руководителя, адрес и телефон не извлечены; press@yu.edu.kz — пресс-служба (иного e-mail не найдено)
 • В вузе модель с вице-президентами: с 14.08.2026 исполнительный вице-президент — Ermek Nurmaganbet, вице-президент по исследованиям — Samal Syrlybekkyzy, по академической работе — Kairbek Makulov
 • По сообщению сайта, вуз впервые вошёл в QS World University Rankings 2026 (позиция не проверена); QS2027 не проверен
-• Космической активности не найдено (быстрая проверка); есть технопарк и Fab Node</t>
+• Космической активности не найдено (быстрая проверка); есть технопарк и Fab Node
+• Перепроверка: Сайт yu.edu.kz открыт 04.10.2026, но страница контактов — шаблон-заглушка без телефонов/e-mail, поиск по WP API имени первого руководителя не дал; данные не изменены</t>
         </is>
       </c>
       <c r="AG41" s="4" t="inlineStr">
@@ -34548,7 +34796,8 @@
       <c r="AF21" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт mahsa.edu.my блокирует доступ (HTTP 403), веб-поиск исчерпан — контактные данные, руководитель и адрес не проверены; заполнить вручную
-• В рейтинге QS2027 не найден; спутников нет (nanosats.csv)</t>
+• В рейтинге QS2027 не найден; спутников нет (nanosats.csv)
+• Перепроверка: 04.10.2026: mahsa.edu.my и www.mahsa.edu.my — HTTP 403; поиск не дал официальных данных о руководстве — данные не изменены</t>
         </is>
       </c>
       <c r="AG21" s="4" t="inlineStr">
@@ -34963,7 +35212,8 @@
           <t>• Страница руководства (segi.edu.my/our-leadership) закрыта Cloudflare (403) — ФИО ректора не подтверждено. В поисковой выдаче встречаются Datin Prof. Dr. Mariani Md Nor (и.о. Vice-Chancellor) и Prof. CHM Dr. Teh Geok Bee — уточнить перед рассылкой
 • Infokd@segi.edu.my и imkd@segi.edu.my — ящики приёма (местные / иностранные студенты) кампуса Kota Damansara; отдельного ящика международного офиса не найдено
 • Глобальными партнёрствами группы занимается Managing Director (Group Operations, Globalisation and Digitalisation) SEGi University &amp; Colleges
-• Космических проектов в nanosats.csv не найдено</t>
+• Космических проектов в nanosats.csv не найдено
+• Перепроверка: Сайты SEGi (university.segi.edu.my — ошибка TLS, www.segi.edu.my — Cloudflare 403) по-прежнему недоступны; данные не изменены</t>
         </is>
       </c>
       <c r="AG24" s="4" t="inlineStr">
@@ -35607,19 +35857,50 @@
       </c>
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="4" t="inlineStr"/>
-      <c r="I29" s="4" t="inlineStr"/>
-      <c r="J29" s="4" t="inlineStr"/>
-      <c r="K29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Universiti Tunku Abdul Rahman, Jalan Universiti, Bandar Barat, 31900 Kampar, Perak, Malaysia (Sungai Long Campus: Jalan Sungai Long, Bandar Sungai Long, Cheras, 43000 Kajang, Selangor)</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>info@utar.edu.my</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Ir. Prof. Dato' Dr. Ewe Hong Tat
+Президент университета
+Общий ящик университета (info@); офис президента — president@utar.edu.my
+Обращение: Dear Prof. Ewe,</t>
+        </is>
+      </c>
       <c r="L29" s="4" t="inlineStr"/>
-      <c r="M29" s="4" t="inlineStr"/>
-      <c r="N29" s="4" t="inlineStr"/>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>info@utar.edu.my</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>+60 5 468 8888 (Kampar); +60 3 9086 0288 (Sungai Long); +60 3 9019 8831 (President's Office)</t>
+        </is>
+      </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
           <t>https://www.utar.edu.my</t>
         </is>
       </c>
-      <c r="P29" s="4" t="inlineStr"/>
-      <c r="Q29" s="4" t="inlineStr"/>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>Ir. Prof. Dato' Dr. Ewe Hong Tat</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
           <t>QS2027: 801–850</t>
@@ -35648,16 +35929,22 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD29" s="4" t="inlineStr"/>
+      <c r="AD29" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE29" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF29" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт utar.edu.my и все поддомены недоступны (сброс соединения / 503), веб-поиск исчерпан — контактные данные, руководитель и адрес не проверены; заполнить вручную
-• Спутников нет (nanosats.csv)</t>
+          <t>• Сайт utar.edu.my напрямую из нашей сети недоступен (сброс соединения); страницы открыты через r.jina.ai 04.10.2026. Страница «Past &amp; Present Presidents» — «Third President (2019–Present)», но шаблон сайта офиса президента датирован 2019 г. — актуальность на 2026 г. желательно перепроверить
+• Офис президента: president@utar.edu.my, тел. 03-9019 8831. Международные связи: Office of International Affairs (oia.utar.edu.my) и Office of VP (Internationalisation and Academic Development, iad.utar.edu.my) — e-mail и руководитель на открытых страницах не отображаются
+• Спутников нет (nanosats.csv)
+• Перепроверка: Сайт utar.edu.my открыт через reader-сервис 04.10.2026: президент (Ewe Hong Tat, с 2019 г.), адреса кампусов, info@utar.edu.my, president@utar.edu.my и телефоны подтверждены; страницы офиса президента и OIA с © 2019, e-mail OIA не опубликован</t>
         </is>
       </c>
       <c r="AG29" s="4" t="inlineStr">
@@ -37363,7 +37650,8 @@
 • Ректор не подтверждён: в WHED указан Vice-Chancellor Mohamad Afzhan Khan, в поисковой выдаче — Prof. Dr. Vincent Oh Kim Seng; уточнить перед рассылкой
 • Адрес — по WHED (IAU); в поисковой выдаче встречается тел. +60 88-448 344 (не проверено)
 • Космических проектов в nanosats.csv не найдено
-• THE 2027: статус Reporter (без ранга)</t>
+• THE 2027: статус Reporter (без ранга)
+• Перепроверка: Сайт jesselton.edu.my по-прежнему за Cloudflare (403), ACBSP тоже 403; поисковая выдача 04.10.2026 называет VC Prof. Dr. Vincent Oh Kim Seng — не подтверждено; данные не изменены</t>
         </is>
       </c>
       <c r="AG41" s="4" t="inlineStr">
@@ -37761,7 +38049,8 @@
 • Личный e-mail ректора на странице: datoazimuddin@nbuc.edu.my; в поисковой выдаче — vc@nbuc.edu.my и admin@nbuc.edu.my (не проверены)
 • Ранее назывался International University College of Technology Twintech (Sabah). Основные направления указаны ориентировочно
 • Космических проектов в nanosats.csv не найдено
-• THE 2027: статус Reporter (без ранга)</t>
+• THE 2027: статус Reporter (без ранга)
+• Перепроверка: nbuc.edu.my показывает «Bot Verification» — данные не изменены (04.10.2026)</t>
         </is>
       </c>
       <c r="AG44" s="4" t="inlineStr">
@@ -40632,14 +40921,16 @@
       <c r="AD13" s="4" t="inlineStr"/>
       <c r="AE13" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF13" s="4" t="inlineStr">
         <is>
           <t>• На сайте не опубликован ни один e-mail; телефон — со страницы Centre for Research and International Programme (CRIP), страница устаревшая (упоминает прежнего ректора)
 • Международные связи — Centre for Research and International Programme (CRIP)
-• Космических проектов не выявлено (nanosats.csv)</t>
+• Космических проектов не выявлено (nanosats.csv)
+• Регистратор: Mrs. Rufina U. Ufiofio (страница Principal Officers)
+• Перепроверка: 04.10.2026: ректор Prof. S. O. Asagba подтверждён на главной и странице Principal Officers; e-mail на сайте по-прежнему не опубликован (страница /contact — 404)</t>
         </is>
       </c>
       <c r="AG13" s="4" t="inlineStr">
@@ -40706,11 +40997,30 @@
           <t>Ekiti State University, Iworoko Road, P.M.B. 5363, Ado-Ekiti, Ekiti State, Nigeria</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>registrar@eksu.edu.ng</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Prof. Joseph Babatola Ayodele
+Ректор (Vice-Chancellor)
+Регистратор (Registrar, Mr. Joseph Ife Oluwole)
+Обращение: Dear Prof. Ayodele,</t>
+        </is>
+      </c>
       <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>registrar@eksu.edu.ng</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>+234 803 855 8350 (Registrar)</t>
+        </is>
+      </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
           <t>https://eksu.edu.ng</t>
@@ -40750,19 +41060,24 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD14" s="4" t="inlineStr"/>
+      <c r="AD14" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE14" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF14" s="4" t="inlineStr">
         <is>
-          <t>• Главная страница eksu.edu.ng за Cloudflare; страница Administration доступна
-• На странице Administration e-mail регистратора закодирован как «registrar@eksu.edu» (вероятно, усечённый registrar@eksu.edu.ng) — не внесён, требует проверки
+          <t>• Главная страница eksu.edu.ng за Cloudflare; страница Administration доступна (дата обновления не указана)
+• E-mail регистратора registrar@eksu.edu.ng взят из ссылки mailto на странице Administration (видимый текст усечён до «registrar@eksu.edu»); регистратор — Mr. Joseph Ife Oluwole (с 10.05.2021)
 • Ректор Prof. Joseph Babatola Ayodele — 9-й ректор, с 20.08.2024
-• Адрес (P.M.B. 5363) — из поисковой выдачи
-• Космических проектов не выявлено (nanosats.csv)</t>
+• Адрес (P.M.B. 5363) — из поисковой выдачи; страница контактов на сайте отсутствует (404). Отдельный офис международных связей не найден
+• Космических проектов не выявлено (nanosats.csv)
+• Перепроверка: Страница Administration повторно открыта 04.10.2026: ректор Prof. J.B. Ayodele (с 20.08.2024) подтверждён; e-mail регистратора декодирован из ссылки mailto — registrar@eksu.edu.ng, добавлен телефон регистратора</t>
         </is>
       </c>
       <c r="AG14" s="4" t="inlineStr">
@@ -40905,7 +41220,8 @@
         <is>
           <t>• Сайт fuoye.edu.ng возвращает 403 — контакты из поисковой выдачи по официальным страницам, требуют проверки
 • Общие адреса по выдаче: info@fuoye.edu.ng, support@fuoye.edu.ng
-• Космических проектов не выявлено (nanosats.csv)</t>
+• Космических проектов не выявлено (nanosats.csv)
+• Перепроверка: Сайт fuoye.edu.ng (включая vc.fuoye.edu.ng) по-прежнему отдаёт 403/антибот-заглушку; данные не изменены</t>
         </is>
       </c>
       <c r="AG15" s="4" t="inlineStr">
@@ -41891,7 +42207,8 @@
 • В выдаче фигурируют общие адреса support@lmu.edu.ng и feedback@lmu.edu.ng (и admissions@) — не подтверждены, в поле не внесены
 • Ректор Prof. Kolawole O. Ajanaku с 01.09.2023 — актуальность на 2026 г. не подтверждена
 • Частный аграрно-ориентированный университет Living Faith Church (как Covenant)
-• Космических проектов не выявлено (nanosats.csv)</t>
+• Космических проектов не выявлено (nanosats.csv)
+• Перепроверка: Сайт lmu.edu.ng по-прежнему недоступен (ошибка TLS / 502 на v4.); ректор Ajanaku подтверждается только выдачей официальной страницы VC — данные не изменены</t>
         </is>
       </c>
       <c r="AG22" s="4" t="inlineStr">
@@ -42165,22 +42482,23 @@
       </c>
       <c r="AE24" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF24" s="4" t="inlineStr">
         <is>
-          <t>• Сайт переделан: на новой странице контактов нет e-mail; info@unizik.edu.ng и P.M.B. 5025 взяты из поисковой выдачи по старой странице — проверить
+          <t>• Info@unizik.edu.ng подтверждён на текущей официальной странице Contact (адрес защищён Cloudflare-обфускацией); P.M.B. 5025 — из старой страницы (поисковая выдача), на новой указано лишь «Awka, Anambra State»
 • Телефон на сайте выглядит как заглушка (+234 (0)46 800 000) — не использован
-• Ректор Prof. Ugochukwu Anyaehie указан на главной странице (после смены руководства в 2025 г.; уточнить, не и.о. ли)
-• Международный офис не найден; космических проектов не выявлено (nanosats.csv)</t>
+• Ректор Prof. Ugochukwu Anyaehie указан на главной странице в блоке «Office of the Vice-Chancellor» (без пометки «Acting»); проректоры: Prof. Alex C. Asigbo (Academic), Prof. Hilda Osisioma (Administration); регистратор — Chinenye Gloria Okeke
+• Международный офис не найден; космических проектов не выявлено (nanosats.csv)
+• Перепроверка: 04.10.2026: ректор и info@unizik.edu.ng подтверждены на официальном сайте (главная и Contact)</t>
         </is>
       </c>
       <c r="AG24" s="4" t="inlineStr">
         <is>
           <t>• Https://unizik.edu.ng/
 • Https://unizik.edu.ng/contact
-• Https://unizik.edu.ng/contact-us/ (search snippet)
+• Https://unizik.edu.ng/contact-us/ (search snippet, P.M.B. 5025)
 • Nanosats.csv</t>
         </is>
       </c>
@@ -42317,7 +42635,8 @@
         <is>
           <t>• Домен oouagoiwoye.edu.ng перенаправляет на портал CCED — официальная главная страница недоступна; контакты из поисковой выдачи, требуют проверки
 • Ректор Prof. Ayodeji Agboola с октября 2022 г. (по данным поиска); регистратор Olufemi Ayodele Ogunwomoju
-• Космических проектов не выявлено (nanosats.csv)</t>
+• Космических проектов не выявлено (nanosats.csv)
+• Перепроверка: Домен oouagoiwoye.edu.ng (все пути) перенаправляет на студенческий портал CCED, portal.oouagoiwoye.edu.ng не содержит контактов и данных о руководстве; данные не изменены</t>
         </is>
       </c>
       <c r="AG25" s="4" t="inlineStr">
@@ -42598,19 +42917,21 @@
       </c>
       <c r="AE27" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF27" s="4" t="inlineStr">
         <is>
-          <t>• Сайт uniben.edu закрыт Cloudflare (403) — контакты взяты из поисковой выдачи по официальной странице, требуют проверки
-• Ректор Prof. Edoba Omoregie, SAN — 11-й ректор UNIBEN
-• Международный офис не найден; космических проектов не выявлено (nanosats.csv)</t>
+          <t>• Сайт uniben.edu закрыт Cloudflare (403) — контакты (registrar@uniben.edu, телефон) взяты из поисковой выдачи по официальной странице, требуют проверки
+• Ректор Prof. Edoba (Bright) Omoregie, SAN — 11-й ректор UNIBEN; подтверждён списком NUC (там с опечаткой «Adoba»); NUC указывает домен uniben.edu.ng
+• Международный офис не найден; космических проектов не выявлено (nanosats.csv)
+• Перепроверка: 04.10.2026: ректор (VC) Prof. Edoba Bright Omoregie подтверждён в официальном списке федеральных вузов NUC; сайт uniben.edu по-прежнему закрыт Cloudflare (403) — e-mail и телефон не подтверждены</t>
         </is>
       </c>
       <c r="AG27" s="4" t="inlineStr">
         <is>
-          <t>• Https://www.uniben.edu/vchancellor.html
+          <t>• Https://www.nuc.edu.ng/nigerian-univerisities/federal-univeristies/
+• Https://www.uniben.edu/vchancellor.html
 • Https://uniben.edu/contact.html (search snippets)
 • Https://en.wikipedia.org/wiki/Edoba_Omoregie
 • Nanosats.csv</t>
@@ -43145,10 +43466,12 @@
       </c>
       <c r="AF31" s="4" t="inlineStr">
         <is>
-          <t>• На сайте не опубликованы e-mail; телефон на главной — заглушка (+234 80 123 1234); страница контактов пустая
+          <t>• Повторная проверка 04.10.2026: на сайте по-прежнему не опубликованы e-mail; телефон в шапке — заглушка (+234 80 123 1234 / 1 800 123 4567); страница contact.php пустая
+• ВК проф. Mohammed Laminu Mele указан на главной и на странице Principal Officers (в должности с 18.09.2024 — по Wikipedia)
 • Нужен иной канал связи (напр., через посольство/NUC)
 • Северо-восток Нигерии (Борно) — регион с проблемами безопасности
-• Космических проектов не выявлено (nanosats.csv)</t>
+• Космических проектов не выявлено (nanosats.csv)
+• Перепроверка: ВК подтверждён на сайте; контактов на сайте по-прежнему нет (заглушки) — данные не изменены</t>
         </is>
       </c>
       <c r="AG31" s="4" t="inlineStr">
@@ -43408,13 +43731,15 @@
       <c r="AD33" s="4" t="inlineStr"/>
       <c r="AE33" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF33" s="4" t="inlineStr">
         <is>
           <t>• Сайт — SPA; данные извлечены из кода сайта; официальный e-mail не опубликован (в коде указан только support@absu.com — не домен вуза, не использован)
-• Международный офис не найден; космических проектов не выявлено (nanosats.csv)</t>
+• Международный офис не найден; космических проектов не выявлено (nanosats.csv)
+• Повторная проверка 04.10.2026: в текущей версии официального сайта (SPA) по-прежнему VC — Prof. Ndukwe Okeudo, тел. +234 901 800 3421; домены absu.edu.ng/portal.absu.edu.ng недоступны; e-mail с доменом вуза не найден
+• Перепроверка: Ректор и телефон подтверждены в текущей версии официального сайта 04.10.2026; официального e-mail по-прежнему нет</t>
         </is>
       </c>
       <c r="AG33" s="4" t="inlineStr">
@@ -43977,7 +44302,8 @@
           <t>• Сайт acu.edu.ng закрыт Cloudflare — контакты взяты из поисковой выдачи по официальным страницам, требуют проверки
 • Prof. Ebunoluwa Oduwole — первая женщина-ректор ACU (назначена в 2025 г.)
 • Частный англиканский университет; международный офис не найден
-• Космических проектов не выявлено (nanosats.csv)</t>
+• Космических проектов не выявлено (nanosats.csv)
+• Перепроверка: acu.edu.ng (включая /contact) закрыт Cloudflare 403 — данные не изменены (04.10.2026)</t>
         </is>
       </c>
       <c r="AG37" s="4" t="inlineStr">
@@ -44387,9 +44713,10 @@
       <c r="AF40" s="4" t="inlineStr">
         <is>
           <t>• Новый частный университет (лицензия 2023, открыт 20.01.2024); основатель/канцлер — генерал-майор в отставке Dr. S. A. Awosanya
-• Официальный сайт недоступен (502), домен aua.edu.ng не подтверждён; e-mail и телефон не найдены (в агрегаторах — номера посредников «по продаже форм», не использованы)
-• Имя ректора — только из поисковой выдачи, не подтверждено
-• Космических проектов нет; приоритет для рассылки низкий</t>
+• Официальный сайт недоступен (домен aua.edu.ng не резолвится / 502), домен не подтверждён; e-mail и телефон не найдены (в агрегаторах — номера посредников «по продаже форм», не использованы)
+• Имя ректора не подтверждено: Prof. Olukayode Dewumi Akinyemi — только из поисковой выдачи (MySchoolGist, 2026); в июне 2024 г. Vice-Chancellor — Prof. Amos Onasanya (Edugist, 18.06.2024) — возможна смена, перепроверить
+• Космических проектов нет; приоритет для рассылки низкий
+• Перепроверка: Сайт aua.edu.ng не резолвится (DNS/502); ректор не подтверждён: в 2024 г. VC был Prof. Amos Onasanya (Edugist, 18.06.2024), Akinyemi — только по сниппету 2026 г</t>
         </is>
       </c>
       <c r="AG40" s="4" t="inlineStr">
@@ -44397,7 +44724,8 @@
           <t>• Https://www.citypeopleonline.com/aletheia-university-takes-off-in-ago-iwoye/
 • Https://thecccworldwide.org/2023/12/alethia-university-berths-at-ago-iwoye-ogun-state/
 • Https://myschoolgist.com/news/aletheia-university-jupeb-approval-188161/ (search snippet)
-• Nanosats.csv</t>
+• Nanosats.csv
+• Https://edugist.org/avoid-destructive-vices-focus-on-your-future-aletheia-university-vc-advises-matriculating-students/</t>
         </is>
       </c>
       <c r="AH40" s="4" t="inlineStr">
@@ -45015,7 +45343,8 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>ФИО не найдено
+          <t>Assoc. Prof. Dr. Panavy Pookaiyaudom
+President
 Международный колледж (Mahanakorn University of Technology International College, MUTIC)
 Обращение: Dear Head of the International Office,</t>
         </is>
@@ -45028,22 +45357,22 @@
       <c r="M3" s="4" t="inlineStr"/>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>+66 61 223 2344</t>
+          <t>+66 2 988 3650 (ext. 1105–1107)</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>https://www.mut.ac.th</t>
+          <t>https://mut.ac.th</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>Prof. Panavy Pookaiyaudom</t>
+          <t>Assoc. Prof. Dr. Panavy Pookaiyaudom (รศ. ดร.ภานวีย์ โภไคยอุดม)</t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>President (อธิการบดี)</t>
         </is>
       </c>
       <c r="R3" s="4" t="inlineStr"/>
@@ -45089,23 +45418,25 @@
       </c>
       <c r="AE3" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF3" s="4" t="inlineStr">
         <is>
-          <t>• Основной сайт www.mut.ac.th недоступен (ошибка TLS / HTTP 503); контакты взяты с сайта международного колледжа MUTIC (inter.mut.ac.th) — inter@mut.ac.th и тел. +66 61 223 2344 относятся к международному колледжу
-• Президент проф. Панави Пукайяудом подтверждён только источником от октября 2024 (визит в Chongqing Jiaotong University); Википедия называет другое имя (Sujate Jantarang) — перепроверить перед отправкой
-• Исторически первый тайский вуз со своим микроспутником TMSAT (Thai Paht-1, 1998), построенным инженерами MUT в Университете Суррея; данные о TMSAT из Википедии, официальную страницу открыть не удалось
-• Частный университет</t>
+          <t>• Сайт mut.ac.th открывается (неполная цепочка сертификата устранена загрузкой промежуточного сертификата Sectigo); на странице «Руководство» (staff-manager, сайт 2025–2026) президент — доц. д-р Панави Пукайяудом; Sujate Jantarang — теперь советник президента
+• Телефон и адрес — со страницы «Контакты» mut.ac.th (общий номер, доб. 1105–1107 — отдел по связям с общественностью); общего e-mail на сайте нет
+• Inter@mut.ac.th — ящик международного колледжа MUTIC из прежней проверки; новый сайт inter.mut.ac.th (2026) e-mail не показывает — перепроверить
+• Исторически первый тайский вуз со своим микроспутником TMSAT (Thai Paht-1, 1998), построенным инженерами MUT в Университете Суррея; данные о TMSAT из Википедии
+• Частный университет
+• Перепроверка: Президент (доц. д-р Панави Пукайяудом), адрес и телефон подтверждены на сайте mut.ac.th 04.10.2026; e-mail MUTIC не подтверждён</t>
         </is>
       </c>
       <c r="AG3" s="4" t="inlineStr">
         <is>
-          <t>• Https://en.wikipedia.org/wiki/Mahanakorn_University_of_Technology
-• Https://inter.mut.ac.th/privacy-policy/
-• Https://inter.mut.ac.th/about-us/
-• Https://www.cqjtu.edu.cn/info/1178/1851.htm</t>
+          <t>• Https://mut.ac.th/staff-manager/
+• Https://mut.ac.th/contact-us/
+• Https://en.wikipedia.org/wiki/Mahanakorn_University_of_Technology
+• Https://inter.mut.ac.th/privacy-policy/</t>
         </is>
       </c>
       <c r="AH3" s="4" t="inlineStr">
@@ -45506,22 +45837,27 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>120 The Government Complex, Ratthaprasasanabhakti Building, 6th–7th Floor, Chaeng Watthana Road, Lak Si, Bangkok 10210, Thailand</t>
+          <t>120 Government Complex Commemorating His Majesty the King's 80th Birthday Anniversary, Ratthaprasasanabhakti Building, 6th–7th Floors, Chaeng Watthana Road, Thung Song Hong, Lak Si, Bangkok 10210, Thailand</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>saraban@gistda.or.th</t>
+          <t>siriluk@gistda.or.th</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>ФИО не найдено
+          <t>Dr. Pakorn Apaphant
+Executive Director (ceo@gistda.or.th, +66 2 141 4450)
 Отдел делопроизводства / официальной корреспонденции (Saraban)
-Обращение: Dear Head of the International Office,</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr"/>
+Обращение: Dear Dr. Apaphant,</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>siriluk@gistda.or.th</t>
+        </is>
+      </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
           <t>saraban@gistda.or.th</t>
@@ -45599,23 +45935,26 @@
       </c>
       <c r="AE6" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF6" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт gistda.or.th был недоступен (HTTP 503 / ошибка TLS); адрес, телефон и e-mail saraban@gistda.or.th взяты из поисковой выдачи по странице контактов GISTDA — перед рассылкой перепроверить
+          <t>• Официальный сайт открывается только по http:// (у https ошибка сертификата); адрес, телефоны 0-2141-4444/4468 и saraban@gistda.or.th подтверждены в подвале главной страницы (новости сентября 2026)
+• Исполнительный директор Pakorn Apaphant, Ph.D. — на официальной странице «Executive Team»: тел. +66 2 141 4450, ceo@gistda.or.th
+• Email_international — заместитель исполнительного директора по стратегическим альянсам (Strategic Alliance Engagement) Siriluk Prukpitikul, Ph.D., тел. +66 2 141 4665; отдельного ящика международного отдела нет
 • GISTDA — национальное космическое агентство Таиланда: владеет и эксплуатирует THEOS (2008) и THEOS-2 (2023), но оба построены Airbus/EADS, поэтому в satellites_launched не засчитаны
 • THEOS-2A (совместная разработка) потерян при аварии PSLV-C62 12.01.2026; THEOS-3 разрабатывается тайскими инженерами
-• Директор д-р Пакорн Апапхан (ปกรณ์ อาภาพันธุ์) упомянут в новости от 4.09.2026
-• 25.08.2026 на Long March-6C выведен GISTDA CubeSat-1 (Lingzhi-09), разработанный китайской GalaxySpace для GISTDA (с наземным сегментом и обучением тайской команды) — не засчитан как собственная разработка; спутник предназначен в т.ч. для обучения студентов тайских вузов</t>
+• 25.08.2026 на Long March-6C выведен GISTDA CubeSat-1 (Lingzhi-09), разработанный китайской GalaxySpace для GISTDA — не засчитан как собственная разработка
+• Перепроверка: Сайт открыт по http 04.10.2026: директор, адрес, телефон и e-mail подтверждены на официальных страницах; добавлены ceo@ и ящик зам. директора по стратегическим альянсам</t>
         </is>
       </c>
       <c r="AG6" s="4" t="inlineStr">
         <is>
-          <t>• Https://en.wikipedia.org/wiki/Geo-Informatics_and_Space_Technology_Development_Agency
+          <t>• Http://www.gistda.or.th/
+• Http://www.gistda.or.th/about/organizational-structure-gistda-board-structure-gistda-executive-team/
+• Https://en.wikipedia.org/wiki/Geo-Informatics_and_Space_Technology_Development_Agency
 • Https://thestandard.co/thailand-space-market-theos3-law/
-• Https://www.gistda.or.th/news_view_new.php?n_id=9176
 • Https://www.mreport.co.th/news/industry-movement/316-kmitl-launches-space-hub-chumporn
 • Https://equalocean.com/news/2026082622141-galaxyspace-completes-first-whole-satellite-delivery-southeast-asia-thai-cubesat</t>
         </is>
@@ -48396,7 +48735,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Sukhumvit 23 Road, Khlong Toei Nuea, Watthana, Bangkok 10110, Thailand</t>
+          <t>114 Sukhumvit 23, Watthana, Bangkok 10110, Thailand</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -48417,10 +48756,14 @@
           <t>ird@g.swu.ac.th</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr"/>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>contact@g.swu.ac.th</t>
+        </is>
+      </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>+66 2 260 1012</t>
+          <t>+66 2 649 5000 (International Relations &amp; Corporate Communication: ext. 15640, 15642, 15666)</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -48428,10 +48771,14 @@
           <t>https://www.swu.ac.th</t>
         </is>
       </c>
-      <c r="P25" s="4" t="inlineStr"/>
+      <c r="P25" s="4" t="inlineStr">
+        <is>
+          <t>Prof. Dr. Chonlawit Jiaratjit (ศาสตราจารย์ ดร.ชลวิทย์ เจียรจิตต์)</t>
+        </is>
+      </c>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>President (อธิการบดี)</t>
         </is>
       </c>
       <c r="R25" s="4" t="inlineStr"/>
@@ -48465,20 +48812,23 @@
       </c>
       <c r="AE25" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF25" s="4" t="inlineStr">
         <is>
-          <t>• Сайт swu.ac.th закрыт защитой Cloudflare (403) — официальные страницы открыть не удалось; квота веб-поиска исчерпана
-• Президент не подтверждён источником 2025–2026 (Википедия называет проф. д-ра Чолвита Джиараджита) — перед отправкой проверить
-• Международный контакт (ird@g.swu.ac.th, тел. +66 2 260 1012) и и.о. проректора по международным связям и коммуникациям доц. Прапапорн Роджсирируч — по списку ASEA-UNINET (дата страницы не указана)
-• Космическая проверка не проведена (квота поиска исчерпана); в nanosats.csv вуз не найден</t>
+          <t>• Основной сайт swu.ac.th закрыт Cloudflare (403), но сайт Офиса президента op.swu.ac.th доступен (2026): президент — проф. д-р Чолвит Джиаратджит, адрес, общий e-mail contact@g.swu.ac.th и телефон подтверждены
+• Отдел международных связей и корпоративных коммуникаций (ส่วนวิเทศสัมพันธ์และสื่อสารองค์กร): доб. 15640/15642/15666, факс +66 2 260 3637 (op.swu.ac.th/contact); прежний номер +66 2 260 1012 не подтверждён и заменён
+• Международный ящик ird@g.swu.ac.th и и.о. проректора по межд. связям доц. Прапапорн Роджсирируч — по списку ASEA-UNINET (дата не указана), на официальных страницах не подтверждены
+• Космическая проверка не проведена (квота поиска исчерпана); в nanosats.csv вуз не найден
+• Перепроверка: Президент, адрес, contact@g.swu.ac.th и телефон подтверждены на op.swu.ac.th 04.10.2026; адресат в межд. отделе не подтверждён</t>
         </is>
       </c>
       <c r="AG25" s="4" t="inlineStr">
         <is>
-          <t>• Https://asea-uninet.org/network-members/member-universities/thai-universities/
+          <t>• Https://op.swu.ac.th/
+• Https://op.swu.ac.th/contact
+• Https://asea-uninet.org/network-members/member-universities/thai-universities/
 • Https://en.wikipedia.org/wiki/Srinakharinwirot_University</t>
         </is>
       </c>
@@ -48981,11 +49331,29 @@
           <t>58 Moo 9, Km. 42, Paholyothin Highway, Klong Luang, Pathum Thani 12120, Thailand</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr"/>
-      <c r="K29" s="4" t="inlineStr"/>
-      <c r="L29" s="4" t="inlineStr"/>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>oia@ait.ac.th</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>ФИО не найдено
+Office of International Affairs (OIA), AIT
+Обращение: Dear Head of the International Office,</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>oia@ait.ac.th</t>
+        </is>
+      </c>
       <c r="M29" s="4" t="inlineStr"/>
-      <c r="N29" s="4" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>+66 2 524 5010</t>
+        </is>
+      </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
           <t>https://www.ait.ac.th</t>
@@ -49021,7 +49389,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD29" s="4" t="inlineStr"/>
+      <c r="AD29" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE29" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
@@ -49029,10 +49401,11 @@
       </c>
       <c r="AF29" s="4" t="inlineStr">
         <is>
-          <t>• Сайт ait.ac.th закрыт Cloudflare (403) — контакты не проверены
-• Адрес по базе WHED (IAU); президент проф. Pai-Chi Li подтверждён публикацией The Nation (май 2026)
+          <t>• Сайт ait.ac.th закрыт Cloudflare (403) — oia@ait.ac.th и +66 2 524 5010 взяты из поисковой выдачи по странице ait.ac.th/contact; перепроверить
+• Адрес по базе WHED (IAU) и выдаче официального сайта (P.O. Box 4); президент проф. Pai-Chi Li подтверждён публикацией The Nation (май 2026)
 • В AIT сильная школа дистанционного зондирования/ГИС — потенциально интересный партнёр
-• Спутников в базе nanosats.csv не найдено</t>
+• Спутников в базе nanosats.csv не найдено
+• Перепроверка: Сайт ait.ac.th по-прежнему закрыт Cloudflare (403); e-mail Office of International Affairs oia@ait.ac.th и телефон внесены по выдаче официальной страницы ait.ac.th/contact — не открыта напрямую</t>
         </is>
       </c>
       <c r="AG29" s="4" t="inlineStr">
@@ -49040,7 +49413,8 @@
           <t>• Https://whed.net/institutions/IAU-014537
 • Https://www.nationthailand.com/pr-news/pr-news/40066406
 • Http://campusupdate.ait.asia/
-• Nanosats.csv</t>
+• Nanosats.csv
+• Https://ait.ac.th/contact/ (search snippet)</t>
         </is>
       </c>
       <c r="AH29" s="4" t="inlineStr">
@@ -49536,7 +49910,7 @@
       <c r="M33" s="4" t="inlineStr"/>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>+66 43 811 128</t>
+          <t>+66 43 811 128 (main line, + 4-digit extension; President's Office ext. 3001/3012); +66 43 602 055</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -49577,22 +49951,26 @@
       <c r="AD33" s="4" t="inlineStr"/>
       <c r="AE33" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF33" s="4" t="inlineStr">
         <is>
-          <t>• E-mail университета/международного отдела на сайте не найден — нужен иной канал (телефон/Facebook)
+          <t>• E-mail университета/международного отдела на официальных сайтах (th./en.ksu.ac.th) не опубликован — нужен иной канал (телефон/Facebook)
 • Ректор подтверждён новостью сайта от 3.10.2026; латинская транслитерация не подтверждена
-• Есть подразделение «งานวิเทศสัมพันธ์» (международные связи), руководитель не указан
+• Телефоны подтверждены на официальном сайте: общий 043-811-128 + добавочный (канцелярия ректора 3001/3012), EN-сайт указывает +66 43 602 055
+• Есть подразделение «งานวิเทศสัมพันธ์» (международные связи), руководитель и телефон не указаны
 • Спутников в базе nanosats.csv не найдено
-• THE2027: участник в статусе Reporter (без места в рейтинге)</t>
+• THE2027: участник в статусе Reporter (без места в рейтинге)
+• Перепроверка: 04.10.2026: ректор и телефоны (в т.ч. добавочные канцелярии ректора) подтверждены на официальном сайте; e-mail по-прежнему не опубликован</t>
         </is>
       </c>
       <c r="AG33" s="4" t="inlineStr">
         <is>
           <t>• Https://th.ksu.ac.th/
 • Https://th.ksu.ac.th/archives/100509
+• Https://en.ksu.ac.th/
+• Https://th.ksu.ac.th/เบอร์โทรศัพท์คณะ-หน่วยง (phone directory)
 • Nanosats.csv</t>
         </is>
       </c>
@@ -50008,7 +50386,8 @@
 • Info@neu.ac.th и телефон взяты с приёмной страницы NEU (idcneu.com) — фактически адрес приёмной комиссии
 • Спутников в базе nanosats.csv не найдено
 • Спутники PROVES-Atlas и THIS-SAT в nanosats.csv принадлежат Northeastern University (США), а не тайскому вузу
-• THE2027: участник в статусе Reporter (без места в рейтинге)</t>
+• THE2027: участник в статусе Reporter (без места в рейтинге)
+• Перепроверка: Сайт neu.ac.th и поддомены по-прежнему закрыты (403 Cloudflare / 502, в т.ч. WebFetch) на 04.10.2026; ректор не подтверждён; данные не изменены</t>
         </is>
       </c>
       <c r="AG36" s="4" t="inlineStr">
@@ -50277,11 +50656,12 @@
       </c>
       <c r="AF38" s="4" t="inlineStr">
         <is>
-          <t>• Основной сайт rmutk.ac.th закрыт защитой Incapsula — контакты университета не проверены
-• Ректор не установлен: по результатам поиска в 2026 г. идёт процедура выбора ректора — уточнить перед рассылкой
+          <t>• Основной сайт rmutk.ac.th по-прежнему закрыт защитой Incapsula (включая WP API) — контакты университета не проверены
+• Ректор не установлен: по поисковому индексу официальной страницы «อธิการบดีและคณะผู้บริหาร» — รศ.ดร.พิชัย จันทร์มณี (Assoc. Prof. Dr. Pichai Chanmanee, pichai.j@mail.rmutk.ac.th), но с 05.2026 идёт процедура выбора нового ректора (приём заявок 4–10.06.2026, Dailynews 20.05.2026) — уточнить перед рассылкой; поле оставлено пустым
 • Isic_ir@mail.rmutk.ac.th — отдел международных связей Института науки, инноваций и культуры (ISIC), а не всего университета
 • Спутников в базе nanosats.csv не найдено
-• THE2027: участник в статусе Reporter (без места в рейтинге)</t>
+• THE2027: участник в статусе Reporter (без места в рейтинге)
+• Перепроверка: Сайт закрыт Incapsula; руководитель не подтверждён (идёт выбор ректора 2026), данные не изменены</t>
         </is>
       </c>
       <c r="AG38" s="4" t="inlineStr">
@@ -50703,7 +51083,7 @@
       </c>
       <c r="AD41" s="4" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="AE41" s="4" t="inlineStr">
